--- a/salidas/empresas/ORCL.xlsx
+++ b/salidas/empresas/ORCL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>9.980511665344238</v>
+        <v>9.980508804321289</v>
       </c>
       <c r="C2" t="n">
         <v>12.56999969482422</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>10.86978530883789</v>
+        <v>10.86978054046631</v>
       </c>
       <c r="C4" t="n">
         <v>13.6899995803833</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>11.58438014984131</v>
+        <v>11.58437919616699</v>
       </c>
       <c r="C5" t="n">
         <v>14.59000015258789</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>11.29060173034668</v>
+        <v>11.29059886932373</v>
       </c>
       <c r="C6" t="n">
         <v>14.22000026702881</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>11.50497817993164</v>
+        <v>11.50497913360596</v>
       </c>
       <c r="C7" t="n">
         <v>14.48999977111816</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.88609409332275</v>
+        <v>11.88610076904297</v>
       </c>
       <c r="C8" t="n">
         <v>14.97000026702881</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43395233154297</v>
+        <v>12.43395042419434</v>
       </c>
       <c r="C9" t="n">
         <v>15.65999984741211</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.08546352386475</v>
+        <v>14.08545875549316</v>
       </c>
       <c r="C10" t="n">
         <v>17.73999977111816</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>14.66507148742676</v>
+        <v>14.66507530212402</v>
       </c>
       <c r="C11" t="n">
         <v>18.46999931335449</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>15.12558841705322</v>
+        <v>15.12559032440186</v>
       </c>
       <c r="C12" t="n">
         <v>19.04999923706055</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>13.60905742645264</v>
+        <v>13.60906505584717</v>
       </c>
       <c r="C13" t="n">
         <v>17.13999938964844</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>13.04532718658447</v>
+        <v>13.04533004760742</v>
       </c>
       <c r="C15" t="n">
         <v>16.43000030517578</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.39511299133301</v>
+        <v>14.39511489868164</v>
       </c>
       <c r="C16" t="n">
         <v>18.1299991607666</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>14.92708969116211</v>
+        <v>14.92709445953369</v>
       </c>
       <c r="C17" t="n">
         <v>18.79999923706055</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>15.38761520385742</v>
+        <v>15.38761043548584</v>
       </c>
       <c r="C18" t="n">
         <v>19.3799991607666</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>15.64962768554688</v>
+        <v>15.64962959289551</v>
       </c>
       <c r="C19" t="n">
         <v>19.70999908447266</v>
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>16.10220146179199</v>
+        <v>16.10220718383789</v>
       </c>
       <c r="C21" t="n">
         <v>20.28000068664551</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>17.18997383117676</v>
+        <v>17.18998146057129</v>
       </c>
       <c r="C22" t="n">
         <v>21.64999961853027</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>17.60285949707031</v>
+        <v>17.60285568237305</v>
       </c>
       <c r="C23" t="n">
         <v>22.17000007629395</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>16.02280807495117</v>
+        <v>16.02280426025391</v>
       </c>
       <c r="C24" t="n">
         <v>20.18000030517578</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.92839431762695</v>
+        <v>17.92839050292969</v>
       </c>
       <c r="C25" t="n">
         <v>22.57999992370605</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>16.31658935546875</v>
+        <v>16.31658172607422</v>
       </c>
       <c r="C26" t="n">
         <v>20.54999923706055</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.92708969116211</v>
+        <v>14.92709445953369</v>
       </c>
       <c r="C27" t="n">
         <v>18.79999923706055</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.53053283691406</v>
+        <v>15.53052997589111</v>
       </c>
       <c r="C28" t="n">
         <v>19.55999946594238</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.55478477478027</v>
+        <v>16.55478096008301</v>
       </c>
       <c r="C29" t="n">
         <v>20.85000038146973</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>18.13484001159668</v>
+        <v>18.13483428955078</v>
       </c>
       <c r="C30" t="n">
         <v>22.84000015258789</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>16.67387962341309</v>
+        <v>16.67388916015625</v>
       </c>
       <c r="C31" t="n">
         <v>21</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.09469604492188</v>
+        <v>17.09470176696777</v>
       </c>
       <c r="C32" t="n">
         <v>21.53000068664551</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>14.52215766906738</v>
+        <v>14.52215576171875</v>
       </c>
       <c r="C35" t="n">
         <v>18.29000091552734</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>12.77536582946777</v>
+        <v>12.77537536621094</v>
       </c>
       <c r="C36" t="n">
         <v>16.09000015258789</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.07752132415771</v>
+        <v>14.0775203704834</v>
       </c>
       <c r="C37" t="n">
         <v>17.72999954223633</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.36292171478271</v>
+        <v>13.3629264831543</v>
       </c>
       <c r="C38" t="n">
         <v>16.82999992370605</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>12.3386697769165</v>
+        <v>12.33867454528809</v>
       </c>
       <c r="C39" t="n">
         <v>15.53999996185303</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.34747791290283</v>
+        <v>14.34747695922852</v>
       </c>
       <c r="C40" t="n">
         <v>18.06999969482422</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.39575290679932</v>
+        <v>15.39575862884521</v>
       </c>
       <c r="C41" t="n">
         <v>19.34000015258789</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>17.05156326293945</v>
+        <v>17.05155372619629</v>
       </c>
       <c r="C43" t="n">
         <v>21.42000007629395</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.65984916687012</v>
+        <v>17.65985107421875</v>
       </c>
       <c r="C44" t="n">
         <v>22.1299991607666</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>17.46035385131836</v>
+        <v>17.46034812927246</v>
       </c>
       <c r="C45" t="n">
         <v>21.8799991607666</v>
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.87847900390625</v>
+        <v>16.87848281860352</v>
       </c>
       <c r="C47" t="n">
         <v>21.10000038146973</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>17.66241455078125</v>
+        <v>17.66241264343262</v>
       </c>
       <c r="C48" t="n">
         <v>22.07999992370605</v>
@@ -1393,7 +1405,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>18.48360824584961</v>
+        <v>18.48359870910645</v>
       </c>
       <c r="C50" t="n">
         <v>23.05999946594238</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>19.75805854797363</v>
+        <v>19.75806427001953</v>
       </c>
       <c r="C51" t="n">
         <v>24.64999961853027</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>20.60769653320312</v>
+        <v>20.60770034790039</v>
       </c>
       <c r="C52" t="n">
         <v>25.70999908447266</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>20.77570343017578</v>
+        <v>20.77570724487305</v>
       </c>
       <c r="C53" t="n">
         <v>25.8700008392334</v>
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.12552833557129</v>
+        <v>18.12553024291992</v>
       </c>
       <c r="C54" t="n">
         <v>22.56999969482422</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>17.23410797119141</v>
+        <v>17.23411178588867</v>
       </c>
       <c r="C55" t="n">
         <v>21.45999908447266</v>
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>19.02552795410156</v>
+        <v>19.02552604675293</v>
       </c>
       <c r="C56" t="n">
         <v>23.63999938964844</v>
@@ -1597,11 +1609,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>17.5768871307373</v>
+        <v>17.57688522338867</v>
       </c>
       <c r="C57" t="n">
         <v>21.84000015258789</v>
@@ -1626,11 +1638,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>21.60894775390625</v>
+        <v>21.60895538330078</v>
       </c>
       <c r="C58" t="n">
         <v>26.85000038146973</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>23.68858337402344</v>
+        <v>23.68857383728027</v>
       </c>
       <c r="C59" t="n">
         <v>29.3799991607666</v>
@@ -1684,11 +1696,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>21.8099422454834</v>
+        <v>21.80993843078613</v>
       </c>
       <c r="C60" t="n">
         <v>27.04999923706055</v>
@@ -1713,11 +1725,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>25.23664474487305</v>
+        <v>25.23664093017578</v>
       </c>
       <c r="C61" t="n">
         <v>31.29999923706055</v>
@@ -1742,11 +1754,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.86670303344727</v>
+        <v>25.8667049407959</v>
       </c>
       <c r="C62" t="n">
         <v>32.02999877929688</v>
@@ -1771,11 +1783,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>26.56930541992188</v>
+        <v>26.56929779052734</v>
       </c>
       <c r="C63" t="n">
         <v>32.90000152587891</v>
@@ -1800,11 +1812,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>26.99731636047363</v>
+        <v>26.99731826782227</v>
       </c>
       <c r="C64" t="n">
         <v>33.43000030517578</v>
@@ -1829,11 +1841,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>29.09253692626953</v>
+        <v>29.09253120422363</v>
       </c>
       <c r="C65" t="n">
         <v>35.95999908447266</v>
@@ -1858,11 +1870,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>27.68482971191406</v>
+        <v>27.6848316192627</v>
       </c>
       <c r="C66" t="n">
         <v>34.22000122070312</v>
@@ -1887,11 +1899,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>26.62500762939453</v>
+        <v>26.62500953674316</v>
       </c>
       <c r="C67" t="n">
         <v>32.90999984741211</v>
@@ -1916,7 +1928,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1945,11 +1957,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>22.74954414367676</v>
+        <v>22.74954032897949</v>
       </c>
       <c r="C69" t="n">
         <v>28.06999969482422</v>
@@ -1974,7 +1986,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -2003,11 +2015,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>26.61179351806641</v>
+        <v>26.61179161071777</v>
       </c>
       <c r="C71" t="n">
         <v>32.77000045776367</v>
@@ -2032,11 +2044,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>25.45864295959473</v>
+        <v>25.45864105224609</v>
       </c>
       <c r="C72" t="n">
         <v>31.35000038146973</v>
@@ -2061,7 +2073,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2090,11 +2102,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>22.95987319946289</v>
+        <v>22.95986747741699</v>
       </c>
       <c r="C74" t="n">
         <v>28.20999908447266</v>
@@ -2119,11 +2131,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>23.80632019042969</v>
+        <v>23.80632591247559</v>
       </c>
       <c r="C75" t="n">
         <v>29.25</v>
@@ -2148,11 +2160,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>23.73307037353516</v>
+        <v>23.73307609558105</v>
       </c>
       <c r="C76" t="n">
         <v>29.15999984741211</v>
@@ -2177,7 +2189,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2206,11 +2218,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>21.58752250671387</v>
+        <v>21.58752059936523</v>
       </c>
       <c r="C78" t="n">
         <v>26.46999931335449</v>
@@ -2235,11 +2247,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>24.22173690795898</v>
+        <v>24.22173881530762</v>
       </c>
       <c r="C79" t="n">
         <v>29.70000076293945</v>
@@ -2264,11 +2276,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>24.68048095703125</v>
+        <v>24.68048477172852</v>
       </c>
       <c r="C80" t="n">
         <v>30.20000076293945</v>
@@ -2293,11 +2305,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.86547470092773</v>
+        <v>25.86547660827637</v>
       </c>
       <c r="C81" t="n">
         <v>31.64999961853027</v>
@@ -2322,11 +2334,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>25.71019554138184</v>
+        <v>25.71019744873047</v>
       </c>
       <c r="C82" t="n">
         <v>31.45999908447266</v>
@@ -2351,11 +2363,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.44947242736816</v>
+        <v>25.44947052001953</v>
       </c>
       <c r="C83" t="n">
         <v>31.07999992370605</v>
@@ -2380,11 +2392,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>26.35019302368164</v>
+        <v>26.35020446777344</v>
       </c>
       <c r="C84" t="n">
         <v>32.18000030517578</v>
@@ -2409,7 +2421,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2438,11 +2450,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>29.23966789245605</v>
+        <v>29.23966026306152</v>
       </c>
       <c r="C86" t="n">
         <v>35.5099983215332</v>
@@ -2467,11 +2479,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>28.19392013549805</v>
+        <v>28.19392395019531</v>
       </c>
       <c r="C87" t="n">
         <v>34.2400016784668</v>
@@ -2496,11 +2508,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.62119102478027</v>
+        <v>26.62118721008301</v>
       </c>
       <c r="C88" t="n">
         <v>32.33000183105469</v>
@@ -2525,11 +2537,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>26.99173164367676</v>
+        <v>26.99172592163086</v>
       </c>
       <c r="C89" t="n">
         <v>32.77999877929688</v>
@@ -2554,11 +2566,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>27.81514739990234</v>
+        <v>27.81515312194824</v>
       </c>
       <c r="C90" t="n">
         <v>33.77999877929688</v>
@@ -2583,11 +2595,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.28724670410156</v>
+        <v>25.28724098205566</v>
       </c>
       <c r="C91" t="n">
         <v>30.70999908447266</v>
@@ -2612,7 +2624,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2641,11 +2653,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>26.33443260192871</v>
+        <v>26.33444404602051</v>
       </c>
       <c r="C93" t="n">
         <v>31.86000061035156</v>
@@ -2670,11 +2682,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>27.41724586486816</v>
+        <v>27.417236328125</v>
       </c>
       <c r="C94" t="n">
         <v>33.16999816894531</v>
@@ -2699,7 +2711,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2728,11 +2740,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>29.27525329589844</v>
+        <v>29.27525901794434</v>
       </c>
       <c r="C96" t="n">
         <v>35.29000091552734</v>
@@ -2757,11 +2769,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.73904609680176</v>
+        <v>31.73904418945312</v>
       </c>
       <c r="C97" t="n">
         <v>38.2599983215332</v>
@@ -2786,7 +2798,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2815,11 +2827,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>32.54740142822266</v>
+        <v>32.54737854003906</v>
       </c>
       <c r="C99" t="n">
         <v>39.11000061035156</v>
@@ -2844,11 +2856,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>34.04535675048828</v>
+        <v>34.04534912109375</v>
       </c>
       <c r="C100" t="n">
         <v>40.90999984741211</v>
@@ -2873,11 +2885,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>34.12182235717773</v>
+        <v>34.12185287475586</v>
       </c>
       <c r="C101" t="n">
         <v>40.88000106811523</v>
@@ -2902,11 +2914,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>35.0733642578125</v>
+        <v>35.07336044311523</v>
       </c>
       <c r="C102" t="n">
         <v>42.02000045776367</v>
@@ -2931,11 +2943,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>33.82967376708984</v>
+        <v>33.82967758178711</v>
       </c>
       <c r="C103" t="n">
         <v>40.52999877929688</v>
@@ -2960,11 +2972,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>33.81098175048828</v>
+        <v>33.81096649169922</v>
       </c>
       <c r="C104" t="n">
         <v>40.38999938964844</v>
@@ -2989,11 +3001,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>34.76528167724609</v>
+        <v>34.76527786254883</v>
       </c>
       <c r="C105" t="n">
         <v>41.52999877929688</v>
@@ -3018,7 +3030,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3047,11 +3059,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>32.79043197631836</v>
+        <v>32.79041290283203</v>
       </c>
       <c r="C107" t="n">
         <v>39.04999923706055</v>
@@ -3076,11 +3088,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>35.61182403564453</v>
+        <v>35.61183166503906</v>
       </c>
       <c r="C108" t="n">
         <v>42.40999984741211</v>
@@ -3105,11 +3117,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>37.7614631652832</v>
+        <v>37.76145553588867</v>
       </c>
       <c r="C109" t="n">
         <v>44.97000122070312</v>
@@ -3134,11 +3146,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>35.27064895629883</v>
+        <v>35.27064514160156</v>
       </c>
       <c r="C110" t="n">
         <v>41.88999938964844</v>
@@ -3163,7 +3175,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3192,11 +3204,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>36.33155822753906</v>
+        <v>36.3315544128418</v>
       </c>
       <c r="C112" t="n">
         <v>43.15000152587891</v>
@@ -3221,11 +3233,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>36.85603713989258</v>
+        <v>36.85602951049805</v>
       </c>
       <c r="C113" t="n">
         <v>43.61999893188477</v>
@@ -3250,11 +3262,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>36.74620056152344</v>
+        <v>36.74619293212891</v>
       </c>
       <c r="C114" t="n">
         <v>43.4900016784668</v>
@@ -3279,11 +3291,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>34.05083847045898</v>
+        <v>34.05085372924805</v>
       </c>
       <c r="C115" t="n">
         <v>40.29999923706055</v>
@@ -3308,7 +3320,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3337,11 +3349,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>31.45551490783691</v>
+        <v>31.45550918579102</v>
       </c>
       <c r="C117" t="n">
         <v>37.09000015258789</v>
@@ -3366,11 +3378,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>30.63287162780762</v>
+        <v>30.63286399841309</v>
       </c>
       <c r="C118" t="n">
         <v>36.11999893188477</v>
@@ -3395,11 +3407,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>33.07059478759766</v>
+        <v>33.07057952880859</v>
       </c>
       <c r="C119" t="n">
         <v>38.84000015258789</v>
@@ -3424,11 +3436,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>33.18126678466797</v>
+        <v>33.18129348754883</v>
       </c>
       <c r="C120" t="n">
         <v>38.97000122070312</v>
@@ -3453,7 +3465,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3482,11 +3494,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>31.04387474060059</v>
+        <v>31.04387283325195</v>
       </c>
       <c r="C122" t="n">
         <v>36.31000137329102</v>
@@ -3511,11 +3523,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>31.44571113586426</v>
+        <v>31.44570732116699</v>
       </c>
       <c r="C123" t="n">
         <v>36.77999877929688</v>
@@ -3540,11 +3552,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>34.97672271728516</v>
+        <v>34.97673034667969</v>
       </c>
       <c r="C124" t="n">
         <v>40.90999984741211</v>
@@ -3569,11 +3581,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>34.20603942871094</v>
+        <v>34.20605087280273</v>
       </c>
       <c r="C125" t="n">
         <v>39.86000061035156</v>
@@ -3598,7 +3610,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3627,11 +3639,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>35.12427139282227</v>
+        <v>35.12426376342773</v>
       </c>
       <c r="C127" t="n">
         <v>40.93000030517578</v>
@@ -3656,11 +3668,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>35.34820175170898</v>
+        <v>35.34822082519531</v>
       </c>
       <c r="C128" t="n">
         <v>41.04000091552734</v>
@@ -3685,7 +3697,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3714,11 +3726,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>33.83230972290039</v>
+        <v>33.83229827880859</v>
       </c>
       <c r="C130" t="n">
         <v>39.27999877929688</v>
@@ -3743,11 +3755,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>33.21976852416992</v>
+        <v>33.21977233886719</v>
       </c>
       <c r="C131" t="n">
         <v>38.41999816894531</v>
@@ -3772,11 +3784,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>34.75018310546875</v>
+        <v>34.75020980834961</v>
       </c>
       <c r="C132" t="n">
         <v>40.18999862670898</v>
@@ -3801,7 +3813,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3830,11 +3842,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>34.81686019897461</v>
+        <v>34.81685638427734</v>
       </c>
       <c r="C134" t="n">
         <v>40.11000061035156</v>
@@ -3859,11 +3871,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>36.96957397460938</v>
+        <v>36.96957778930664</v>
       </c>
       <c r="C135" t="n">
         <v>42.59000015258789</v>
@@ -3888,11 +3900,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>38.72300720214844</v>
+        <v>38.72299957275391</v>
       </c>
       <c r="C136" t="n">
         <v>44.61000061035156</v>
@@ -3917,11 +3929,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>39.1949577331543</v>
+        <v>39.19497299194336</v>
       </c>
       <c r="C137" t="n">
         <v>44.95999908447266</v>
@@ -3946,11 +3958,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>39.5698127746582</v>
+        <v>39.56982421875</v>
       </c>
       <c r="C138" t="n">
         <v>45.38999938964844</v>
@@ -3975,11 +3987,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>43.71075820922852</v>
+        <v>43.71074295043945</v>
       </c>
       <c r="C139" t="n">
         <v>50.13999938964844</v>
@@ -4004,11 +4016,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>43.69187927246094</v>
+        <v>43.69186401367188</v>
       </c>
       <c r="C140" t="n">
         <v>49.93000030517578</v>
@@ -4033,11 +4045,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>44.04189300537109</v>
+        <v>44.04190826416016</v>
       </c>
       <c r="C141" t="n">
         <v>50.33000183105469</v>
@@ -4062,7 +4074,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4091,11 +4103,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>44.71636581420898</v>
+        <v>44.71636199951172</v>
       </c>
       <c r="C143" t="n">
         <v>50.90000152587891</v>
@@ -4120,11 +4132,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>43.09990310668945</v>
+        <v>43.09989929199219</v>
       </c>
       <c r="C144" t="n">
         <v>49.06000137329102</v>
@@ -4149,7 +4161,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4178,11 +4190,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>45.4990348815918</v>
+        <v>45.49903106689453</v>
       </c>
       <c r="C146" t="n">
         <v>51.59000015258789</v>
@@ -4207,11 +4219,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>44.68764495849609</v>
+        <v>44.68764877319336</v>
       </c>
       <c r="C147" t="n">
         <v>50.66999816894531</v>
@@ -4236,11 +4248,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>40.34853744506836</v>
+        <v>40.34852600097656</v>
       </c>
       <c r="C148" t="n">
         <v>45.75</v>
@@ -4265,11 +4277,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>40.44474029541016</v>
+        <v>40.44473648071289</v>
       </c>
       <c r="C149" t="n">
         <v>45.66999816894531</v>
@@ -4294,11 +4306,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>41.37460327148438</v>
+        <v>41.37461090087891</v>
       </c>
       <c r="C150" t="n">
         <v>46.72000122070312</v>
@@ -4323,11 +4335,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>39.01894760131836</v>
+        <v>39.01895141601562</v>
       </c>
       <c r="C151" t="n">
         <v>44.06000137329102</v>
@@ -4352,11 +4364,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>42.39038848876953</v>
+        <v>42.3903923034668</v>
       </c>
       <c r="C152" t="n">
         <v>47.68000030517578</v>
@@ -4381,11 +4393,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>43.19054794311523</v>
+        <v>43.19055557250977</v>
       </c>
       <c r="C153" t="n">
         <v>48.58000183105469</v>
@@ -4410,11 +4422,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>45.83995056152344</v>
+        <v>45.8399543762207</v>
       </c>
       <c r="C154" t="n">
         <v>51.56000137329102</v>
@@ -4439,11 +4451,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>43.59653854370117</v>
+        <v>43.59653091430664</v>
       </c>
       <c r="C155" t="n">
         <v>48.84000015258789</v>
@@ -4468,7 +4480,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4497,11 +4509,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>40.30269241333008</v>
+        <v>40.30269622802734</v>
       </c>
       <c r="C157" t="n">
         <v>45.15000152587891</v>
@@ -4526,11 +4538,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>45.01481628417969</v>
+        <v>45.01482391357422</v>
       </c>
       <c r="C158" t="n">
         <v>50.22999954223633</v>
@@ -4555,11 +4567,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>46.7175407409668</v>
+        <v>46.71754455566406</v>
       </c>
       <c r="C159" t="n">
         <v>52.13000106811523</v>
@@ -4584,11 +4596,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>48.13350677490234</v>
+        <v>48.13351058959961</v>
       </c>
       <c r="C160" t="n">
         <v>53.70999908447266</v>
@@ -4613,11 +4625,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>49.80738067626953</v>
+        <v>49.807373046875</v>
       </c>
       <c r="C161" t="n">
         <v>55.33000183105469</v>
@@ -4642,11 +4654,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>45.54946517944336</v>
+        <v>45.54947280883789</v>
       </c>
       <c r="C162" t="n">
         <v>50.59999847412109</v>
@@ -4671,7 +4683,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4700,11 +4712,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>50.88570022583008</v>
+        <v>50.88569641113281</v>
       </c>
       <c r="C164" t="n">
         <v>56.29999923706055</v>
@@ -4729,11 +4741,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>47.0534553527832</v>
+        <v>47.05345916748047</v>
       </c>
       <c r="C165" t="n">
         <v>52.06000137329102</v>
@@ -4758,11 +4770,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>49.73782348632812</v>
+        <v>49.73783493041992</v>
       </c>
       <c r="C166" t="n">
         <v>55.02999877929688</v>
@@ -4787,11 +4799,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>49.46943283081055</v>
+        <v>49.46942520141602</v>
       </c>
       <c r="C167" t="n">
         <v>54.4900016784668</v>
@@ -4816,11 +4828,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>50.96740341186523</v>
+        <v>50.96739959716797</v>
       </c>
       <c r="C168" t="n">
         <v>56.13999938964844</v>
@@ -4845,11 +4857,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>48.09854888916016</v>
+        <v>48.09855651855469</v>
       </c>
       <c r="C169" t="n">
         <v>52.97999954223633</v>
@@ -4874,11 +4886,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>47.82933807373047</v>
+        <v>47.8293342590332</v>
       </c>
       <c r="C170" t="n">
         <v>52.45000076293945</v>
@@ -4903,11 +4915,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>45.10273742675781</v>
+        <v>45.10274887084961</v>
       </c>
       <c r="C171" t="n">
         <v>49.45999908447266</v>
@@ -4932,11 +4944,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>44.07229614257812</v>
+        <v>44.07229232788086</v>
       </c>
       <c r="C172" t="n">
         <v>48.33000183105469</v>
@@ -4961,11 +4973,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>48.53299713134766</v>
+        <v>48.53300094604492</v>
       </c>
       <c r="C173" t="n">
         <v>52.97000122070312</v>
@@ -4990,11 +5002,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>49.26598739624023</v>
+        <v>49.2659912109375</v>
       </c>
       <c r="C174" t="n">
         <v>53.77000045776367</v>
@@ -5019,11 +5031,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>50.64033508300781</v>
+        <v>50.64033889770508</v>
       </c>
       <c r="C175" t="n">
         <v>55.27000045776367</v>
@@ -5048,7 +5060,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5077,7 +5089,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5106,11 +5118,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>54.93050765991211</v>
+        <v>54.93051147460938</v>
       </c>
       <c r="C178" t="n">
         <v>59.70000076293945</v>
@@ -5135,7 +5147,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5164,11 +5176,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>53.32374572753906</v>
+        <v>53.3237419128418</v>
       </c>
       <c r="C180" t="n">
         <v>57.72000122070312</v>
@@ -5193,11 +5205,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>59.76286697387695</v>
+        <v>59.76287078857422</v>
       </c>
       <c r="C181" t="n">
         <v>64.69000244140625</v>
@@ -5222,11 +5234,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>56.04096221923828</v>
+        <v>56.04096603393555</v>
       </c>
       <c r="C182" t="n">
         <v>60.43000030517578</v>
@@ -5251,11 +5263,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>59.82462310791016</v>
+        <v>59.82463073730469</v>
       </c>
       <c r="C183" t="n">
         <v>64.51000213623047</v>
@@ -5280,11 +5292,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>65.07355499267578</v>
+        <v>65.07353210449219</v>
       </c>
       <c r="C184" t="n">
         <v>70.16999816894531</v>
@@ -5309,11 +5321,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>70.58943939208984</v>
+        <v>70.58946228027344</v>
       </c>
       <c r="C185" t="n">
         <v>75.79000091552734</v>
@@ -5338,11 +5350,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>73.33702850341797</v>
+        <v>73.33704376220703</v>
       </c>
       <c r="C186" t="n">
         <v>78.73999786376953</v>
@@ -5367,7 +5379,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5396,7 +5408,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5425,11 +5437,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>83.32033538818359</v>
+        <v>83.32032775878906</v>
       </c>
       <c r="C189" t="n">
         <v>89.12999725341797</v>
@@ -5454,11 +5466,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>81.45068359375</v>
+        <v>81.45069885253906</v>
       </c>
       <c r="C190" t="n">
         <v>87.12999725341797</v>
@@ -5483,11 +5495,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>89.9984130859375</v>
+        <v>89.99843597412109</v>
       </c>
       <c r="C191" t="n">
         <v>95.94000244140625</v>
@@ -5512,7 +5524,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5541,11 +5553,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>81.80907440185547</v>
+        <v>81.80906677246094</v>
       </c>
       <c r="C193" t="n">
         <v>87.20999908447266</v>
@@ -5570,11 +5582,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>76.41658782958984</v>
+        <v>76.41658020019531</v>
       </c>
       <c r="C194" t="n">
         <v>81.16000366210938</v>
@@ -5599,11 +5611,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>71.5299072265625</v>
+        <v>71.52989959716797</v>
       </c>
       <c r="C195" t="n">
         <v>75.97000122070312</v>
@@ -5628,11 +5640,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>77.89482116699219</v>
+        <v>77.89483642578125</v>
       </c>
       <c r="C196" t="n">
         <v>82.73000335693359</v>
@@ -5657,11 +5669,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>69.38046264648438</v>
+        <v>69.38047027587891</v>
       </c>
       <c r="C197" t="n">
         <v>73.40000152587891</v>
@@ -5686,7 +5698,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5715,11 +5727,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>66.04377746582031</v>
+        <v>66.04378509521484</v>
       </c>
       <c r="C199" t="n">
         <v>69.87000274658203</v>
@@ -5744,11 +5756,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>73.90640258789062</v>
+        <v>73.90639495849609</v>
       </c>
       <c r="C200" t="n">
         <v>77.83999633789062</v>
@@ -5773,7 +5785,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5802,7 +5814,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5831,7 +5843,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5860,11 +5872,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>79.23935699462891</v>
+        <v>79.23936462402344</v>
       </c>
       <c r="C204" t="n">
         <v>83.02999877929688</v>
@@ -5889,11 +5901,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>78.00826263427734</v>
+        <v>78.00823974609375</v>
       </c>
       <c r="C205" t="n">
         <v>81.73999786376953</v>
@@ -5918,11 +5930,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>84.73802185058594</v>
+        <v>84.738037109375</v>
       </c>
       <c r="C206" t="n">
         <v>88.45999908447266</v>
@@ -5947,11 +5959,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>83.72262573242188</v>
+        <v>83.72263336181641</v>
       </c>
       <c r="C207" t="n">
         <v>87.40000152587891</v>
@@ -5976,11 +5988,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>89.01036834716797</v>
+        <v>89.01038360595703</v>
       </c>
       <c r="C208" t="n">
         <v>92.91999816894531</v>
@@ -6005,7 +6017,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6034,11 +6046,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>101.9075012207031</v>
+        <v>101.9075317382812</v>
       </c>
       <c r="C210" t="n">
         <v>105.9400024414062</v>
@@ -6063,11 +6075,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>114.5569686889648</v>
+        <v>114.5569763183594</v>
       </c>
       <c r="C211" t="n">
         <v>119.0899963378906</v>
@@ -6092,11 +6104,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>113.1635360717773</v>
+        <v>113.1635437011719</v>
       </c>
       <c r="C212" t="n">
         <v>117.2300033569336</v>
@@ -6121,11 +6133,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>116.2138977050781</v>
+        <v>116.2139053344727</v>
       </c>
       <c r="C213" t="n">
         <v>120.3899993896484</v>
@@ -6150,11 +6162,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>102.2458419799805</v>
+        <v>102.2458572387695</v>
       </c>
       <c r="C214" t="n">
         <v>105.9199981689453</v>
@@ -6179,11 +6191,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>100.1785125732422</v>
+        <v>100.1785049438477</v>
       </c>
       <c r="C215" t="n">
         <v>103.4000015258789</v>
@@ -6208,11 +6220,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>112.5894012451172</v>
+        <v>112.5893936157227</v>
       </c>
       <c r="C216" t="n">
         <v>116.2099990844727</v>
@@ -6237,11 +6249,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>102.145263671875</v>
+        <v>102.1452560424805</v>
       </c>
       <c r="C217" t="n">
         <v>105.4300003051758</v>
@@ -6266,11 +6278,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>108.6392440795898</v>
+        <v>108.6392517089844</v>
       </c>
       <c r="C218" t="n">
         <v>111.6999969482422</v>
@@ -6295,11 +6307,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>108.6197967529297</v>
+        <v>108.6197891235352</v>
       </c>
       <c r="C219" t="n">
         <v>111.6800003051758</v>
@@ -6324,11 +6336,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>122.1681060791016</v>
+        <v>122.168098449707</v>
       </c>
       <c r="C220" t="n">
         <v>125.6100006103516</v>
@@ -6353,7 +6365,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6382,7 +6394,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6411,11 +6423,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>137.7740783691406</v>
+        <v>137.7741088867188</v>
       </c>
       <c r="C223" t="n">
         <v>141.1999969482422</v>
@@ -6440,7 +6452,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6469,7 +6481,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6498,7 +6510,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6527,7 +6539,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6556,7 +6568,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6585,7 +6597,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6614,7 +6626,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6643,7 +6655,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6672,11 +6684,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>137.4475860595703</v>
+        <v>137.4476165771484</v>
       </c>
       <c r="C232" t="n">
         <v>139.8099975585938</v>
@@ -6701,11 +6713,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>138.8391723632812</v>
+        <v>138.8391876220703</v>
       </c>
       <c r="C233" t="n">
         <v>140.7200012207031</v>
@@ -6730,7 +6742,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6759,11 +6771,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>215.7078704833984</v>
+        <v>215.7078857421875</v>
       </c>
       <c r="C235" t="n">
         <v>218.6300048828125</v>
@@ -6788,7 +6800,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6817,7 +6829,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6846,7 +6858,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6875,11 +6887,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>260.1011657714844</v>
+        <v>260.1011962890625</v>
       </c>
       <c r="C239" t="n">
         <v>262.6099853515625</v>
@@ -6904,7 +6916,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6933,7 +6945,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6962,7 +6974,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6991,7 +7003,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7020,7 +7032,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7049,7 +7061,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7078,7 +7090,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7107,7 +7119,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7136,7 +7148,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7165,7 +7177,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7194,32 +7206,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>144.5599975585938</v>
+        <v>139.5399932861328</v>
       </c>
       <c r="C250" t="n">
-        <v>144.5599975585938</v>
+        <v>139.5399932861328</v>
       </c>
       <c r="D250" t="n">
-        <v>552785400</v>
+        <v>609358700</v>
       </c>
       <c r="E250" t="n">
         <v>6.38</v>
       </c>
       <c r="F250" t="n">
-        <v>22.65830682736579</v>
+        <v>21.87147230190169</v>
       </c>
       <c r="G250" t="n">
         <v>3023736000</v>
       </c>
       <c r="H250" t="n">
-        <v>437111268777.832</v>
+        <v>421932101139.0381</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1828153648334378</v>
+        <v>0.2015251000748743</v>
       </c>
     </row>
   </sheetData>
@@ -7251,75 +7263,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39600</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39691</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40077</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7355,13 +7367,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39692</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39782</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40169</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7397,13 +7409,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39783</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39872</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40266</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7439,13 +7451,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39873</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39964</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7472,7 +7484,7 @@
       <c r="I5" t="n">
         <v>1.09</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="K5" t="n">
@@ -7485,13 +7497,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39965</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40077</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7518,7 +7530,7 @@
       <c r="I6" t="n">
         <v>1.1</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="K6" t="n">
@@ -7531,13 +7543,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40057</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40169</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7564,7 +7576,7 @@
       <c r="I7" t="n">
         <v>1.14</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="K7" t="n">
@@ -7577,13 +7589,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40148</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40237</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40266</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7610,7 +7622,7 @@
       <c r="I8" t="n">
         <v>1.11</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="K8" t="n">
@@ -7623,13 +7635,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40238</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40329</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7656,7 +7668,7 @@
       <c r="I9" t="n">
         <v>1.21</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="K9" t="n">
@@ -7669,13 +7681,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40330</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40421</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40450</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7702,7 +7714,7 @@
       <c r="I10" t="n">
         <v>1.26</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40450</v>
       </c>
       <c r="K10" t="n">
@@ -7715,13 +7727,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40422</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40533</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7748,7 +7760,7 @@
       <c r="I11" t="n">
         <v>1.34</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40533</v>
       </c>
       <c r="K11" t="n">
@@ -7761,13 +7773,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40513</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40631</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7794,7 +7806,7 @@
       <c r="I12" t="n">
         <v>1.52</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40631</v>
       </c>
       <c r="K12" t="n">
@@ -7807,13 +7819,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40603</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40694</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40722</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7840,7 +7852,7 @@
       <c r="I13" t="n">
         <v>1.67</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40722</v>
       </c>
       <c r="K13" t="n">
@@ -7853,13 +7865,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40695</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40786</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40809</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7886,7 +7898,7 @@
       <c r="I14" t="n">
         <v>1.76</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40809</v>
       </c>
       <c r="K14" t="n">
@@ -7899,13 +7911,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40787</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40877</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40900</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7932,7 +7944,7 @@
       <c r="I15" t="n">
         <v>1.82</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40900</v>
       </c>
       <c r="K15" t="n">
@@ -7945,13 +7957,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40878</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40968</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40991</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7978,7 +7990,7 @@
       <c r="I16" t="n">
         <v>1.9</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40991</v>
       </c>
       <c r="K16" t="n">
@@ -7991,13 +8003,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40969</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41060</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41086</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8024,7 +8036,7 @@
       <c r="I17" t="n">
         <v>1.96</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41086</v>
       </c>
       <c r="K17" t="n">
@@ -8037,13 +8049,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41176</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8070,7 +8082,7 @@
       <c r="I18" t="n">
         <v>2.01</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41176</v>
       </c>
       <c r="K18" t="n">
@@ -8083,13 +8095,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41153</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41264</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8116,7 +8128,7 @@
       <c r="I19" t="n">
         <v>2.11</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41264</v>
       </c>
       <c r="K19" t="n">
@@ -8129,13 +8141,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41244</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41355</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8162,7 +8174,7 @@
       <c r="I20" t="n">
         <v>2.14</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41355</v>
       </c>
       <c r="K20" t="n">
@@ -8175,13 +8187,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41451</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8208,7 +8220,7 @@
       <c r="I21" t="n">
         <v>2.26</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41451</v>
       </c>
       <c r="K21" t="n">
@@ -8221,13 +8233,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41426</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41517</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41537</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8254,7 +8266,7 @@
       <c r="I22" t="n">
         <v>2.32</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41537</v>
       </c>
       <c r="K22" t="n">
@@ -8267,13 +8279,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41518</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41608</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41628</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8300,7 +8312,7 @@
       <c r="I23" t="n">
         <v>2.35</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41628</v>
       </c>
       <c r="K23" t="n">
@@ -8313,13 +8325,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41609</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41698</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41718</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8346,7 +8358,7 @@
       <c r="I24" t="n">
         <v>2.39</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41718</v>
       </c>
       <c r="K24" t="n">
@@ -8359,13 +8371,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41699</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41790</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41816</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8392,7 +8404,7 @@
       <c r="I25" t="n">
         <v>2.38</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41816</v>
       </c>
       <c r="K25" t="n">
@@ -8405,13 +8417,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41791</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41882</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41905</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8438,7 +8450,7 @@
       <c r="I26" t="n">
         <v>2.39</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41905</v>
       </c>
       <c r="K26" t="n">
@@ -8451,13 +8463,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41883</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41973</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41992</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8484,7 +8496,7 @@
       <c r="I27" t="n">
         <v>2.39</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41992</v>
       </c>
       <c r="K27" t="n">
@@ -8497,13 +8509,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41974</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42063</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42082</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8530,7 +8542,7 @@
       <c r="I28" t="n">
         <v>2.39</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42082</v>
       </c>
       <c r="K28" t="n">
@@ -8543,13 +8555,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42064</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42155</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42180</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8576,7 +8588,7 @@
       <c r="I29" t="n">
         <v>2.21</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42180</v>
       </c>
       <c r="K29" t="n">
@@ -8589,13 +8601,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42156</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42247</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42265</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8622,7 +8634,7 @@
       <c r="I30" t="n">
         <v>2.13</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42265</v>
       </c>
       <c r="K30" t="n">
@@ -8635,13 +8647,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42248</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8668,7 +8680,7 @@
       <c r="I31" t="n">
         <v>2.08</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="K31" t="n">
@@ -8681,13 +8693,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42339</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42429</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42447</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8714,7 +8726,7 @@
       <c r="I32" t="n">
         <v>2.02</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42447</v>
       </c>
       <c r="K32" t="n">
@@ -8727,13 +8739,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42430</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42521</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42543</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8760,7 +8772,7 @@
       <c r="I33" t="n">
         <v>2.07</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42543</v>
       </c>
       <c r="K33" t="n">
@@ -8773,13 +8785,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42522</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42613</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42632</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8806,7 +8818,7 @@
       <c r="I34" t="n">
         <v>2.1</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42632</v>
       </c>
       <c r="K34" t="n">
@@ -8819,13 +8831,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42614</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42704</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42723</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8852,7 +8864,7 @@
       <c r="I35" t="n">
         <v>2.069999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42723</v>
       </c>
       <c r="K35" t="n">
@@ -8865,13 +8877,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42705</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42794</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42811</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8898,7 +8910,7 @@
       <c r="I36" t="n">
         <v>2.1</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42811</v>
       </c>
       <c r="K36" t="n">
@@ -8911,13 +8923,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42795</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42886</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42913</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8944,7 +8956,7 @@
       <c r="I37" t="n">
         <v>2.21</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42913</v>
       </c>
       <c r="K37" t="n">
@@ -8957,13 +8969,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42887</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42978</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42996</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8990,7 +9002,7 @@
       <c r="I38" t="n">
         <v>2.3</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42996</v>
       </c>
       <c r="K38" t="n">
@@ -9003,13 +9015,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43069</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43087</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9036,7 +9048,7 @@
       <c r="I39" t="n">
         <v>2.34</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43087</v>
       </c>
       <c r="K39" t="n">
@@ -9049,13 +9061,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43159</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43180</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9082,7 +9094,7 @@
       <c r="I40" t="n">
         <v>0.8300000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43180</v>
       </c>
       <c r="K40" t="n">
@@ -9095,13 +9107,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43160</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43251</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9128,7 +9140,7 @@
       <c r="I41" t="n">
         <v>0.9</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="K41" t="n">
@@ -9141,13 +9153,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43362</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9174,7 +9186,7 @@
       <c r="I42" t="n">
         <v>0.95</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43362</v>
       </c>
       <c r="K42" t="n">
@@ -9187,13 +9199,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43344</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43453</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9220,7 +9232,7 @@
       <c r="I43" t="n">
         <v>1.04</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43453</v>
       </c>
       <c r="K43" t="n">
@@ -9233,13 +9245,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43435</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43524</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43542</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9266,7 +9278,7 @@
       <c r="I44" t="n">
         <v>2.78</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43542</v>
       </c>
       <c r="K44" t="n">
@@ -9279,13 +9291,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9312,7 +9324,7 @@
       <c r="I45" t="n">
         <v>2.97</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="K45" t="n">
@@ -9325,13 +9337,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43617</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43708</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9358,7 +9370,7 @@
       <c r="I46" t="n">
         <v>3.03</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="K46" t="n">
@@ -9371,13 +9383,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43709</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9404,7 +9416,7 @@
       <c r="I47" t="n">
         <v>3.11</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="K47" t="n">
@@ -9417,13 +9429,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43800</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9450,7 +9462,7 @@
       <c r="I48" t="n">
         <v>3.14</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="K48" t="n">
@@ -9463,13 +9475,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43891</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43982</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44004</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9496,7 +9508,7 @@
       <c r="I49" t="n">
         <v>3.08</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44004</v>
       </c>
       <c r="K49" t="n">
@@ -9509,13 +9521,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43983</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44089</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9542,7 +9554,7 @@
       <c r="I50" t="n">
         <v>3.17</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44089</v>
       </c>
       <c r="K50" t="n">
@@ -9555,13 +9567,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44075</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9588,7 +9600,7 @@
       <c r="I51" t="n">
         <v>3.28</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="K51" t="n">
@@ -9601,13 +9613,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44166</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44255</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44266</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9634,7 +9646,7 @@
       <c r="I52" t="n">
         <v>4.17</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44266</v>
       </c>
       <c r="K52" t="n">
@@ -9647,13 +9659,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44256</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44347</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44368</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9680,7 +9692,7 @@
       <c r="I53" t="n">
         <v>4.55</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44368</v>
       </c>
       <c r="K53" t="n">
@@ -9693,13 +9705,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44348</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44452</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9726,7 +9738,7 @@
       <c r="I54" t="n">
         <v>4.69</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44452</v>
       </c>
       <c r="K54" t="n">
@@ -9739,13 +9751,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44440</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9772,7 +9784,7 @@
       <c r="I55" t="n">
         <v>3.43</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="K55" t="n">
@@ -9785,13 +9797,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44620</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9818,7 +9830,7 @@
       <c r="I56" t="n">
         <v>2.59</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="K56" t="n">
@@ -9831,13 +9843,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44712</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44733</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9864,7 +9876,7 @@
       <c r="I57" t="n">
         <v>2.41</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44733</v>
       </c>
       <c r="K57" t="n">
@@ -9877,13 +9889,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44713</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44804</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44817</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9910,7 +9922,7 @@
       <c r="I58" t="n">
         <v>2.11</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44817</v>
       </c>
       <c r="K58" t="n">
@@ -9923,13 +9935,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44805</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44895</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44908</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9956,7 +9968,7 @@
       <c r="I59" t="n">
         <v>3.2</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44908</v>
       </c>
       <c r="K59" t="n">
@@ -9969,13 +9981,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44896</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44985</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -10002,7 +10014,7 @@
       <c r="I60" t="n">
         <v>3.04</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="K60" t="n">
@@ -10015,13 +10027,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45077</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45097</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10048,7 +10060,7 @@
       <c r="I61" t="n">
         <v>3.07</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45097</v>
       </c>
       <c r="K61" t="n">
@@ -10061,13 +10073,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45078</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45169</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45181</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10094,7 +10106,7 @@
       <c r="I62" t="n">
         <v>3.37</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45181</v>
       </c>
       <c r="K62" t="n">
@@ -10107,13 +10119,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45272</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10140,7 +10152,7 @@
       <c r="I63" t="n">
         <v>3.63</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45272</v>
       </c>
       <c r="K63" t="n">
@@ -10153,13 +10165,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45351</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45363</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10186,7 +10198,7 @@
       <c r="I64" t="n">
         <v>3.8</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45363</v>
       </c>
       <c r="K64" t="n">
@@ -10199,13 +10211,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10232,7 +10244,7 @@
       <c r="I65" t="n">
         <v>3.71</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="K65" t="n">
@@ -10245,13 +10257,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45444</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45535</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10278,7 +10290,7 @@
       <c r="I66" t="n">
         <v>3.88</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="K66" t="n">
@@ -10291,13 +10303,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45536</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45626</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10324,7 +10336,7 @@
       <c r="I67" t="n">
         <v>4.09</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="K67" t="n">
@@ -10337,13 +10349,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45627</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45727</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10370,7 +10382,7 @@
       <c r="I68" t="n">
         <v>4.26</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45727</v>
       </c>
       <c r="K68" t="n">
@@ -10383,13 +10395,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45717</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45808</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10416,7 +10428,7 @@
       <c r="I69" t="n">
         <v>4.34</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="K69" t="n">
@@ -10429,13 +10441,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45809</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10462,7 +10474,7 @@
       <c r="I70" t="n">
         <v>4.32</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="K70" t="n">
@@ -10475,13 +10487,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46002</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10508,7 +10520,7 @@
       <c r="I71" t="n">
         <v>5.32</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46002</v>
       </c>
       <c r="K71" t="n">
@@ -10521,13 +10533,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10554,7 +10566,7 @@
       <c r="I72" t="n">
         <v>5.57</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="K72" t="n">
@@ -10567,13 +10579,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46195</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10600,7 +10612,7 @@
       <c r="I73" t="n">
         <v>5.83</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46195</v>
       </c>
       <c r="K73" t="n">
@@ -10613,13 +10625,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46174</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46265</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10646,7 +10658,7 @@
       <c r="I74" t="n">
         <v>6.38</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="K74" t="n">
@@ -10683,52 +10695,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40072</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40077</v>
       </c>
       <c r="C2" t="n">
@@ -10757,10 +10769,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40162</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40169</v>
       </c>
       <c r="C3" t="n">
@@ -10789,10 +10801,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40260</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40266</v>
       </c>
       <c r="C4" t="n">
@@ -10821,10 +10833,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40351</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="C5" t="n">
@@ -10853,10 +10865,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40434</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40450</v>
       </c>
       <c r="C6" t="n">
@@ -10885,10 +10897,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40525</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40533</v>
       </c>
       <c r="C7" t="n">
@@ -10917,10 +10929,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40623</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40631</v>
       </c>
       <c r="C8" t="n">
@@ -10949,10 +10961,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40714</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40722</v>
       </c>
       <c r="C9" t="n">
@@ -10981,10 +10993,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40802</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40809</v>
       </c>
       <c r="C10" t="n">
@@ -11013,10 +11025,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40893</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40900</v>
       </c>
       <c r="C11" t="n">
@@ -11045,10 +11057,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40987</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40991</v>
       </c>
       <c r="C12" t="n">
@@ -11077,10 +11089,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41080</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41086</v>
       </c>
       <c r="C13" t="n">
@@ -11109,10 +11121,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41257</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41264</v>
       </c>
       <c r="C14" t="n">
@@ -11141,10 +11153,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41348</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41355</v>
       </c>
       <c r="C15" t="n">
@@ -11173,10 +11185,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41444</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41451</v>
       </c>
       <c r="C16" t="n">
@@ -11205,10 +11217,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41530</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41537</v>
       </c>
       <c r="C17" t="n">
@@ -11237,10 +11249,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41621</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41628</v>
       </c>
       <c r="C18" t="n">
@@ -11269,10 +11281,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41711</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41718</v>
       </c>
       <c r="C19" t="n">
@@ -11301,10 +11313,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41809</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41816</v>
       </c>
       <c r="C20" t="n">
@@ -11333,10 +11345,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41898</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41905</v>
       </c>
       <c r="C21" t="n">
@@ -11365,10 +11377,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41985</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41992</v>
       </c>
       <c r="C22" t="n">
@@ -11397,10 +11409,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42075</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42082</v>
       </c>
       <c r="C23" t="n">
@@ -11429,10 +11441,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42173</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42180</v>
       </c>
       <c r="C24" t="n">
@@ -11461,10 +11473,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42258</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42265</v>
       </c>
       <c r="C25" t="n">
@@ -11493,10 +11505,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42349</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="C26" t="n">
@@ -11525,10 +11537,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42440</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42447</v>
       </c>
       <c r="C27" t="n">
@@ -11557,10 +11569,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42536</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42543</v>
       </c>
       <c r="C28" t="n">
@@ -11589,10 +11601,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42625</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42632</v>
       </c>
       <c r="C29" t="n">
@@ -11621,10 +11633,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42716</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42723</v>
       </c>
       <c r="C30" t="n">
@@ -11653,10 +11665,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42807</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42811</v>
       </c>
       <c r="C31" t="n">
@@ -11685,10 +11697,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42902</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42913</v>
       </c>
       <c r="C32" t="n">
@@ -11717,10 +11729,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42989</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42996</v>
       </c>
       <c r="C33" t="n">
@@ -11749,10 +11761,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43080</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43087</v>
       </c>
       <c r="C34" t="n">
@@ -11781,10 +11793,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43174</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43180</v>
       </c>
       <c r="C35" t="n">
@@ -11813,10 +11825,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43266</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="C36" t="n">
@@ -11845,10 +11857,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43356</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43362</v>
       </c>
       <c r="C37" t="n">
@@ -11877,10 +11889,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43448</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43453</v>
       </c>
       <c r="C38" t="n">
@@ -11909,10 +11921,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43537</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43542</v>
       </c>
       <c r="C39" t="n">
@@ -11941,10 +11953,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43633</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="C40" t="n">
@@ -11973,10 +11985,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43718</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="C41" t="n">
@@ -12005,10 +12017,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43808</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="C42" t="n">
@@ -12037,10 +12049,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43899</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="C43" t="n">
@@ -12069,10 +12081,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43998</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44004</v>
       </c>
       <c r="C44" t="n">
@@ -12101,10 +12113,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44078</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44089</v>
       </c>
       <c r="C45" t="n">
@@ -12133,10 +12145,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44169</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="C46" t="n">
@@ -12165,10 +12177,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44260</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44266</v>
       </c>
       <c r="C47" t="n">
@@ -12197,10 +12209,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44362</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44368</v>
       </c>
       <c r="C48" t="n">
@@ -12229,10 +12241,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44445</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44452</v>
       </c>
       <c r="C49" t="n">
@@ -12261,10 +12273,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44536</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="C50" t="n">
@@ -12293,10 +12305,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44627</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="C51" t="n">
@@ -12325,10 +12337,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44725</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44733</v>
       </c>
       <c r="C52" t="n">
@@ -12357,10 +12369,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44812</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44817</v>
       </c>
       <c r="C53" t="n">
@@ -12389,10 +12401,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44902</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44908</v>
       </c>
       <c r="C54" t="n">
@@ -12421,10 +12433,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44991</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="C55" t="n">
@@ -12453,10 +12465,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45097</v>
       </c>
       <c r="C56" t="n">
@@ -12485,10 +12497,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45176</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45181</v>
       </c>
       <c r="C57" t="n">
@@ -12517,10 +12529,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45267</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45272</v>
       </c>
       <c r="C58" t="n">
@@ -12549,10 +12561,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45358</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45363</v>
       </c>
       <c r="C59" t="n">
@@ -12581,10 +12593,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45456</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="C60" t="n">
@@ -12613,10 +12625,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45541</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="C61" t="n">
@@ -12645,10 +12657,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45632</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="C62" t="n">
@@ -12677,10 +12689,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45723</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45727</v>
       </c>
       <c r="C63" t="n">
@@ -12709,10 +12721,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45821</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="C64" t="n">
@@ -12741,10 +12753,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45905</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="C65" t="n">
@@ -12773,10 +12785,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45996</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46002</v>
       </c>
       <c r="C66" t="n">
@@ -12805,10 +12817,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46086</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="C67" t="n">
@@ -12837,10 +12849,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46185</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46195</v>
       </c>
       <c r="C68" t="n">
@@ -12869,10 +12881,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="C69" t="n">
@@ -12919,12 +12931,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/ORCL.xlsx
+++ b/salidas/empresas/ORCL.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>9.980508804321289</v>
+        <v>9.980509757995605</v>
       </c>
       <c r="C2" t="n">
         <v>12.56999969482422</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>9.861410140991211</v>
+        <v>9.861411094665527</v>
       </c>
       <c r="C3" t="n">
         <v>12.42000007629395</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>10.86978054046631</v>
+        <v>10.86978340148926</v>
       </c>
       <c r="C4" t="n">
         <v>13.6899995803833</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>11.29059886932373</v>
+        <v>11.29059791564941</v>
       </c>
       <c r="C6" t="n">
         <v>14.22000026702881</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>11.50497913360596</v>
+        <v>11.50497817993164</v>
       </c>
       <c r="C7" t="n">
         <v>14.48999977111816</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.88610076904297</v>
+        <v>11.88609313964844</v>
       </c>
       <c r="C8" t="n">
         <v>14.97000026702881</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43395042419434</v>
+        <v>12.43395137786865</v>
       </c>
       <c r="C9" t="n">
         <v>15.65999984741211</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.08545875549316</v>
+        <v>14.08545970916748</v>
       </c>
       <c r="C10" t="n">
         <v>17.73999977111816</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>14.66507530212402</v>
+        <v>14.66507816314697</v>
       </c>
       <c r="C11" t="n">
         <v>18.46999931335449</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>15.12559032440186</v>
+        <v>15.12559604644775</v>
       </c>
       <c r="C12" t="n">
         <v>19.04999923706055</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>13.60906505584717</v>
+        <v>13.6090612411499</v>
       </c>
       <c r="C13" t="n">
         <v>17.13999938964844</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>13.6249475479126</v>
+        <v>13.62494277954102</v>
       </c>
       <c r="C14" t="n">
         <v>17.15999984741211</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>13.04533004760742</v>
+        <v>13.04532718658447</v>
       </c>
       <c r="C15" t="n">
         <v>16.43000030517578</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.39511489868164</v>
+        <v>14.39512538909912</v>
       </c>
       <c r="C16" t="n">
         <v>18.1299991607666</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>14.92709445953369</v>
+        <v>14.92709350585938</v>
       </c>
       <c r="C17" t="n">
         <v>18.79999923706055</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>15.38761043548584</v>
+        <v>15.38760280609131</v>
       </c>
       <c r="C18" t="n">
         <v>19.3799991607666</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>15.64962959289551</v>
+        <v>15.64963436126709</v>
       </c>
       <c r="C19" t="n">
         <v>19.70999908447266</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>15.18117046356201</v>
+        <v>15.1811695098877</v>
       </c>
       <c r="C20" t="n">
         <v>19.1200008392334</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>17.60285568237305</v>
+        <v>17.60286521911621</v>
       </c>
       <c r="C23" t="n">
         <v>22.17000007629395</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>16.02280426025391</v>
+        <v>16.02280616760254</v>
       </c>
       <c r="C24" t="n">
         <v>20.18000030517578</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.92839050292969</v>
+        <v>17.92839813232422</v>
       </c>
       <c r="C25" t="n">
         <v>22.57999992370605</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.92709445953369</v>
+        <v>14.92709350585938</v>
       </c>
       <c r="C27" t="n">
         <v>18.79999923706055</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.53052997589111</v>
+        <v>15.53053283691406</v>
       </c>
       <c r="C28" t="n">
         <v>19.55999946594238</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.55478096008301</v>
+        <v>16.55478286743164</v>
       </c>
       <c r="C29" t="n">
         <v>20.85000038146973</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>18.13483428955078</v>
+        <v>18.13483810424805</v>
       </c>
       <c r="C30" t="n">
         <v>22.84000015258789</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>16.67388916015625</v>
+        <v>16.67388343811035</v>
       </c>
       <c r="C31" t="n">
         <v>21</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.09470176696777</v>
+        <v>17.09469795227051</v>
       </c>
       <c r="C32" t="n">
         <v>21.53000068664551</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.41230010986328</v>
+        <v>17.41229438781738</v>
       </c>
       <c r="C33" t="n">
         <v>21.93000030517578</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>16.12602424621582</v>
+        <v>16.12602996826172</v>
       </c>
       <c r="C34" t="n">
         <v>20.30999946594238</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>12.77537536621094</v>
+        <v>12.77536964416504</v>
       </c>
       <c r="C36" t="n">
         <v>16.09000015258789</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.0775203704834</v>
+        <v>14.07752227783203</v>
       </c>
       <c r="C37" t="n">
         <v>17.72999954223633</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.3629264831543</v>
+        <v>13.36292743682861</v>
       </c>
       <c r="C38" t="n">
         <v>16.82999992370605</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>12.33867454528809</v>
+        <v>12.3386754989624</v>
       </c>
       <c r="C39" t="n">
         <v>15.53999996185303</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.34747695922852</v>
+        <v>14.3474760055542</v>
       </c>
       <c r="C40" t="n">
         <v>18.06999969482422</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.39575862884521</v>
+        <v>15.39575481414795</v>
       </c>
       <c r="C41" t="n">
         <v>19.34000015258789</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>17.05155372619629</v>
+        <v>17.05155181884766</v>
       </c>
       <c r="C43" t="n">
         <v>21.42000007629395</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.65985107421875</v>
+        <v>17.65985298156738</v>
       </c>
       <c r="C44" t="n">
         <v>22.1299991607666</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>16.63042259216309</v>
+        <v>16.63042640686035</v>
       </c>
       <c r="C46" t="n">
         <v>20.84000015258789</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.87848281860352</v>
+        <v>16.87848091125488</v>
       </c>
       <c r="C47" t="n">
         <v>21.10000038146973</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>17.66241264343262</v>
+        <v>17.66240501403809</v>
       </c>
       <c r="C48" t="n">
         <v>22.07999992370605</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.62223434448242</v>
+        <v>19.62224006652832</v>
       </c>
       <c r="C49" t="n">
         <v>24.53000068664551</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>18.48359870910645</v>
+        <v>18.48360443115234</v>
       </c>
       <c r="C50" t="n">
         <v>23.05999946594238</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>19.75806427001953</v>
+        <v>19.7580623626709</v>
       </c>
       <c r="C51" t="n">
         <v>24.64999961853027</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>20.60770034790039</v>
+        <v>20.60769462585449</v>
       </c>
       <c r="C52" t="n">
         <v>25.70999908447266</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>20.77570724487305</v>
+        <v>20.77569770812988</v>
       </c>
       <c r="C53" t="n">
         <v>25.8700008392334</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.12553024291992</v>
+        <v>18.12553787231445</v>
       </c>
       <c r="C54" t="n">
         <v>22.56999969482422</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>17.23411178588867</v>
+        <v>17.23412132263184</v>
       </c>
       <c r="C55" t="n">
         <v>21.45999908447266</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>19.02552604675293</v>
+        <v>19.0255298614502</v>
       </c>
       <c r="C56" t="n">
         <v>23.63999938964844</v>
@@ -1613,7 +1613,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>17.57688522338867</v>
+        <v>17.5768871307373</v>
       </c>
       <c r="C57" t="n">
         <v>21.84000015258789</v>
@@ -1642,7 +1642,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>21.60895538330078</v>
+        <v>21.60894584655762</v>
       </c>
       <c r="C58" t="n">
         <v>26.85000038146973</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>23.68857383728027</v>
+        <v>23.68857574462891</v>
       </c>
       <c r="C59" t="n">
         <v>29.3799991607666</v>
@@ -1729,7 +1729,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>25.23664093017578</v>
+        <v>25.23664283752441</v>
       </c>
       <c r="C61" t="n">
         <v>31.29999923706055</v>
@@ -1758,7 +1758,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.8667049407959</v>
+        <v>25.86670303344727</v>
       </c>
       <c r="C62" t="n">
         <v>32.02999877929688</v>
@@ -1787,7 +1787,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>26.56929779052734</v>
+        <v>26.56930351257324</v>
       </c>
       <c r="C63" t="n">
         <v>32.90000152587891</v>
@@ -1816,7 +1816,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>26.99731826782227</v>
+        <v>26.997314453125</v>
       </c>
       <c r="C64" t="n">
         <v>33.43000030517578</v>
@@ -1845,7 +1845,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>29.09253120422363</v>
+        <v>29.09252738952637</v>
       </c>
       <c r="C65" t="n">
         <v>35.95999908447266</v>
@@ -1874,7 +1874,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>27.6848316192627</v>
+        <v>27.68482971191406</v>
       </c>
       <c r="C66" t="n">
         <v>34.22000122070312</v>
@@ -1903,7 +1903,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>26.62500953674316</v>
+        <v>26.62502288818359</v>
       </c>
       <c r="C67" t="n">
         <v>32.90999984741211</v>
@@ -1932,7 +1932,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>24.78378677368164</v>
+        <v>24.7837963104248</v>
       </c>
       <c r="C68" t="n">
         <v>30.57999992370605</v>
@@ -1961,7 +1961,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>22.74954032897949</v>
+        <v>22.74954223632812</v>
       </c>
       <c r="C69" t="n">
         <v>28.06999969482422</v>
@@ -1990,7 +1990,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>23.29254913330078</v>
+        <v>23.29255676269531</v>
       </c>
       <c r="C70" t="n">
         <v>28.73999977111816</v>
@@ -2019,7 +2019,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>26.61179161071777</v>
+        <v>26.61179542541504</v>
       </c>
       <c r="C71" t="n">
         <v>32.77000045776367</v>
@@ -2077,7 +2077,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>20.82980155944824</v>
+        <v>20.82979774475098</v>
       </c>
       <c r="C73" t="n">
         <v>25.64999961853027</v>
@@ -2106,7 +2106,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>22.95986747741699</v>
+        <v>22.95987319946289</v>
       </c>
       <c r="C74" t="n">
         <v>28.20999908447266</v>
@@ -2164,7 +2164,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>23.73307609558105</v>
+        <v>23.73307037353516</v>
       </c>
       <c r="C76" t="n">
         <v>29.15999984741211</v>
@@ -2193,7 +2193,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>23.97707176208496</v>
+        <v>23.97707557678223</v>
       </c>
       <c r="C77" t="n">
         <v>29.39999961853027</v>
@@ -2222,7 +2222,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>21.58752059936523</v>
+        <v>21.58752250671387</v>
       </c>
       <c r="C78" t="n">
         <v>26.46999931335449</v>
@@ -2251,7 +2251,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>24.22173881530762</v>
+        <v>24.22173309326172</v>
       </c>
       <c r="C79" t="n">
         <v>29.70000076293945</v>
@@ -2309,7 +2309,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.86547660827637</v>
+        <v>25.86547088623047</v>
       </c>
       <c r="C81" t="n">
         <v>31.64999961853027</v>
@@ -2338,7 +2338,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>25.71019744873047</v>
+        <v>25.7101993560791</v>
       </c>
       <c r="C82" t="n">
         <v>31.45999908447266</v>
@@ -2367,7 +2367,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.44947052001953</v>
+        <v>25.44947814941406</v>
       </c>
       <c r="C83" t="n">
         <v>31.07999992370605</v>
@@ -2396,7 +2396,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>26.35020446777344</v>
+        <v>26.35019493103027</v>
       </c>
       <c r="C84" t="n">
         <v>32.18000030517578</v>
@@ -2425,7 +2425,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>27.43637084960938</v>
+        <v>27.43637657165527</v>
       </c>
       <c r="C85" t="n">
         <v>33.31999969482422</v>
@@ -2454,7 +2454,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>29.23966026306152</v>
+        <v>29.23966217041016</v>
       </c>
       <c r="C86" t="n">
         <v>35.5099983215332</v>
@@ -2483,7 +2483,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>28.19392395019531</v>
+        <v>28.19391822814941</v>
       </c>
       <c r="C87" t="n">
         <v>34.2400016784668</v>
@@ -2512,7 +2512,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.62118721008301</v>
+        <v>26.62119483947754</v>
       </c>
       <c r="C88" t="n">
         <v>32.33000183105469</v>
@@ -2541,7 +2541,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>26.99172592163086</v>
+        <v>26.99172782897949</v>
       </c>
       <c r="C89" t="n">
         <v>32.77999877929688</v>
@@ -2570,7 +2570,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>27.81515312194824</v>
+        <v>27.81514739990234</v>
       </c>
       <c r="C90" t="n">
         <v>33.77999877929688</v>
@@ -2599,7 +2599,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.28724098205566</v>
+        <v>25.28724479675293</v>
       </c>
       <c r="C91" t="n">
         <v>30.70999908447266</v>
@@ -2628,7 +2628,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>26.73945426940918</v>
+        <v>26.73945808410645</v>
       </c>
       <c r="C92" t="n">
         <v>32.34999847412109</v>
@@ -2657,7 +2657,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>26.33444404602051</v>
+        <v>26.33443641662598</v>
       </c>
       <c r="C93" t="n">
         <v>31.86000061035156</v>
@@ -2686,7 +2686,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>27.417236328125</v>
+        <v>27.41724014282227</v>
       </c>
       <c r="C94" t="n">
         <v>33.16999816894531</v>
@@ -2715,7 +2715,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>27.79033851623535</v>
+        <v>27.79033660888672</v>
       </c>
       <c r="C95" t="n">
         <v>33.5</v>
@@ -2744,7 +2744,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>29.27525901794434</v>
+        <v>29.27525329589844</v>
       </c>
       <c r="C96" t="n">
         <v>35.29000091552734</v>
@@ -2773,7 +2773,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.73904418945312</v>
+        <v>31.73904991149902</v>
       </c>
       <c r="C97" t="n">
         <v>38.2599983215332</v>
@@ -2802,7 +2802,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>30.70822715759277</v>
+        <v>30.70823669433594</v>
       </c>
       <c r="C98" t="n">
         <v>36.90000152587891</v>
@@ -2831,7 +2831,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>32.54737854003906</v>
+        <v>32.54740905761719</v>
       </c>
       <c r="C99" t="n">
         <v>39.11000061035156</v>
@@ -2860,7 +2860,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>34.04534912109375</v>
+        <v>34.04535675048828</v>
       </c>
       <c r="C100" t="n">
         <v>40.90999984741211</v>
@@ -2889,7 +2889,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>34.12185287475586</v>
+        <v>34.12181091308594</v>
       </c>
       <c r="C101" t="n">
         <v>40.88000106811523</v>
@@ -2947,7 +2947,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>33.82967758178711</v>
+        <v>33.82968902587891</v>
       </c>
       <c r="C103" t="n">
         <v>40.52999877929688</v>
@@ -2976,7 +2976,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>33.81096649169922</v>
+        <v>33.81097030639648</v>
       </c>
       <c r="C104" t="n">
         <v>40.38999938964844</v>
@@ -3005,7 +3005,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>34.76527786254883</v>
+        <v>34.76528167724609</v>
       </c>
       <c r="C105" t="n">
         <v>41.52999877929688</v>
@@ -3034,7 +3034,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>32.0446662902832</v>
+        <v>32.04467391967773</v>
       </c>
       <c r="C106" t="n">
         <v>38.27999877929688</v>
@@ -3092,7 +3092,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>35.61183166503906</v>
+        <v>35.61182022094727</v>
       </c>
       <c r="C108" t="n">
         <v>42.40999984741211</v>
@@ -3121,7 +3121,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>37.76145553588867</v>
+        <v>37.76145935058594</v>
       </c>
       <c r="C109" t="n">
         <v>44.97000122070312</v>
@@ -3150,7 +3150,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>35.27064514160156</v>
+        <v>35.27065277099609</v>
       </c>
       <c r="C110" t="n">
         <v>41.88999938964844</v>
@@ -3179,7 +3179,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>36.89567947387695</v>
+        <v>36.89568328857422</v>
       </c>
       <c r="C111" t="n">
         <v>43.81999969482422</v>
@@ -3208,7 +3208,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>36.3315544128418</v>
+        <v>36.33156967163086</v>
       </c>
       <c r="C112" t="n">
         <v>43.15000152587891</v>
@@ -3266,7 +3266,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>36.74619293212891</v>
+        <v>36.74618148803711</v>
       </c>
       <c r="C114" t="n">
         <v>43.4900016784668</v>
@@ -3295,7 +3295,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>34.05085372924805</v>
+        <v>34.05083847045898</v>
       </c>
       <c r="C115" t="n">
         <v>40.29999923706055</v>
@@ -3324,7 +3324,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>33.8725700378418</v>
+        <v>33.87255477905273</v>
       </c>
       <c r="C116" t="n">
         <v>39.93999862670898</v>
@@ -3353,7 +3353,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>31.45550918579102</v>
+        <v>31.45551872253418</v>
       </c>
       <c r="C117" t="n">
         <v>37.09000015258789</v>
@@ -3382,7 +3382,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>30.63286399841309</v>
+        <v>30.63286972045898</v>
       </c>
       <c r="C118" t="n">
         <v>36.11999893188477</v>
@@ -3411,7 +3411,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>33.07057952880859</v>
+        <v>33.07058334350586</v>
       </c>
       <c r="C119" t="n">
         <v>38.84000015258789</v>
@@ -3440,7 +3440,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>33.18129348754883</v>
+        <v>33.18127059936523</v>
       </c>
       <c r="C120" t="n">
         <v>38.97000122070312</v>
@@ -3469,7 +3469,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>31.10371780395508</v>
+        <v>31.10371398925781</v>
       </c>
       <c r="C121" t="n">
         <v>36.52999877929688</v>
@@ -3498,7 +3498,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>31.04387283325195</v>
+        <v>31.04386901855469</v>
       </c>
       <c r="C122" t="n">
         <v>36.31000137329102</v>
@@ -3527,7 +3527,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>31.44570732116699</v>
+        <v>31.44569396972656</v>
       </c>
       <c r="C123" t="n">
         <v>36.77999877929688</v>
@@ -3556,7 +3556,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>34.97673034667969</v>
+        <v>34.97672653198242</v>
       </c>
       <c r="C124" t="n">
         <v>40.90999984741211</v>
@@ -3585,7 +3585,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>34.20605087280273</v>
+        <v>34.20604705810547</v>
       </c>
       <c r="C125" t="n">
         <v>39.86000061035156</v>
@@ -3614,7 +3614,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>34.4978141784668</v>
+        <v>34.49782180786133</v>
       </c>
       <c r="C126" t="n">
         <v>40.20000076293945</v>
@@ -3643,7 +3643,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>35.12426376342773</v>
+        <v>35.124267578125</v>
       </c>
       <c r="C127" t="n">
         <v>40.93000030517578</v>
@@ -3672,7 +3672,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>35.34822082519531</v>
+        <v>35.34821701049805</v>
       </c>
       <c r="C128" t="n">
         <v>41.04000091552734</v>
@@ -3701,7 +3701,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>35.50324630737305</v>
+        <v>35.50324249267578</v>
       </c>
       <c r="C129" t="n">
         <v>41.22000122070312</v>
@@ -3759,7 +3759,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>33.21977233886719</v>
+        <v>33.21976470947266</v>
       </c>
       <c r="C131" t="n">
         <v>38.41999816894531</v>
@@ -3788,7 +3788,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>34.75020980834961</v>
+        <v>34.75019073486328</v>
       </c>
       <c r="C132" t="n">
         <v>40.18999862670898</v>
@@ -3817,7 +3817,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>33.24571228027344</v>
+        <v>33.24570846557617</v>
       </c>
       <c r="C133" t="n">
         <v>38.45000076293945</v>
@@ -3846,7 +3846,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>34.81685638427734</v>
+        <v>34.81685256958008</v>
       </c>
       <c r="C134" t="n">
         <v>40.11000061035156</v>
@@ -3875,7 +3875,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>36.96957778930664</v>
+        <v>36.96958541870117</v>
       </c>
       <c r="C135" t="n">
         <v>42.59000015258789</v>
@@ -3904,7 +3904,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>38.72299957275391</v>
+        <v>38.72299575805664</v>
       </c>
       <c r="C136" t="n">
         <v>44.61000061035156</v>
@@ -3933,7 +3933,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>39.19497299194336</v>
+        <v>39.19496536254883</v>
       </c>
       <c r="C137" t="n">
         <v>44.95999908447266</v>
@@ -3991,7 +3991,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>43.71074295043945</v>
+        <v>43.71075057983398</v>
       </c>
       <c r="C139" t="n">
         <v>50.13999938964844</v>
@@ -4020,7 +4020,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>43.69186401367188</v>
+        <v>43.69186019897461</v>
       </c>
       <c r="C140" t="n">
         <v>49.93000030517578</v>
@@ -4049,7 +4049,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>44.04190826416016</v>
+        <v>44.04189300537109</v>
       </c>
       <c r="C141" t="n">
         <v>50.33000183105469</v>
@@ -4078,7 +4078,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>42.30927276611328</v>
+        <v>42.30926513671875</v>
       </c>
       <c r="C142" t="n">
         <v>48.34999847412109</v>
@@ -4107,7 +4107,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>44.71636199951172</v>
+        <v>44.71636581420898</v>
       </c>
       <c r="C143" t="n">
         <v>50.90000152587891</v>
@@ -4165,7 +4165,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>41.53614044189453</v>
+        <v>41.53612899780273</v>
       </c>
       <c r="C145" t="n">
         <v>47.27999877929688</v>
@@ -4223,7 +4223,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>44.68764877319336</v>
+        <v>44.68765258789062</v>
       </c>
       <c r="C147" t="n">
         <v>50.66999816894531</v>
@@ -4252,7 +4252,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>40.34852600097656</v>
+        <v>40.34853744506836</v>
       </c>
       <c r="C148" t="n">
         <v>45.75</v>
@@ -4281,7 +4281,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>40.44473648071289</v>
+        <v>40.44473266601562</v>
       </c>
       <c r="C149" t="n">
         <v>45.66999816894531</v>
@@ -4397,7 +4397,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>43.19055557250977</v>
+        <v>43.19054412841797</v>
       </c>
       <c r="C153" t="n">
         <v>48.58000183105469</v>
@@ -4426,7 +4426,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>45.8399543762207</v>
+        <v>45.83995819091797</v>
       </c>
       <c r="C154" t="n">
         <v>51.56000137329102</v>
@@ -4455,7 +4455,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>43.59653091430664</v>
+        <v>43.59652709960938</v>
       </c>
       <c r="C155" t="n">
         <v>48.84000015258789</v>
@@ -4484,7 +4484,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>43.52511215209961</v>
+        <v>43.52511596679688</v>
       </c>
       <c r="C156" t="n">
         <v>48.7599983215332</v>
@@ -4542,7 +4542,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>45.01482391357422</v>
+        <v>45.01481246948242</v>
       </c>
       <c r="C158" t="n">
         <v>50.22999954223633</v>
@@ -4571,7 +4571,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>46.71754455566406</v>
+        <v>46.71755218505859</v>
       </c>
       <c r="C159" t="n">
         <v>52.13000106811523</v>
@@ -4600,7 +4600,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>48.13351058959961</v>
+        <v>48.13349533081055</v>
       </c>
       <c r="C160" t="n">
         <v>53.70999908447266</v>
@@ -4629,7 +4629,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>49.807373046875</v>
+        <v>49.80738067626953</v>
       </c>
       <c r="C161" t="n">
         <v>55.33000183105469</v>
@@ -4687,7 +4687,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>51.28368759155273</v>
+        <v>51.28367614746094</v>
       </c>
       <c r="C163" t="n">
         <v>56.97000122070312</v>
@@ -4745,7 +4745,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>47.05345916748047</v>
+        <v>47.05344772338867</v>
       </c>
       <c r="C165" t="n">
         <v>52.06000137329102</v>
@@ -4774,7 +4774,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>49.73783493041992</v>
+        <v>49.73781967163086</v>
       </c>
       <c r="C166" t="n">
         <v>55.02999877929688</v>
@@ -4832,7 +4832,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>50.96739959716797</v>
+        <v>50.9674072265625</v>
       </c>
       <c r="C168" t="n">
         <v>56.13999938964844</v>
@@ -4861,7 +4861,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>48.09855651855469</v>
+        <v>48.09855270385742</v>
       </c>
       <c r="C169" t="n">
         <v>52.97999954223633</v>
@@ -4890,7 +4890,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>47.8293342590332</v>
+        <v>47.82932662963867</v>
       </c>
       <c r="C170" t="n">
         <v>52.45000076293945</v>
@@ -4919,7 +4919,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>45.10274887084961</v>
+        <v>45.10274124145508</v>
       </c>
       <c r="C171" t="n">
         <v>49.45999908447266</v>
@@ -4948,7 +4948,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>44.07229232788086</v>
+        <v>44.07228851318359</v>
       </c>
       <c r="C172" t="n">
         <v>48.33000183105469</v>
@@ -4977,7 +4977,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>48.53300094604492</v>
+        <v>48.53300476074219</v>
       </c>
       <c r="C173" t="n">
         <v>52.97000122070312</v>
@@ -5006,7 +5006,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>49.2659912109375</v>
+        <v>49.26597595214844</v>
       </c>
       <c r="C174" t="n">
         <v>53.77000045776367</v>
@@ -5035,7 +5035,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>50.64033889770508</v>
+        <v>50.64034652709961</v>
       </c>
       <c r="C175" t="n">
         <v>55.27000045776367</v>
@@ -5093,7 +5093,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>52.64863586425781</v>
+        <v>52.64863967895508</v>
       </c>
       <c r="C177" t="n">
         <v>57.22000122070312</v>
@@ -5122,7 +5122,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>54.93051147460938</v>
+        <v>54.93050765991211</v>
       </c>
       <c r="C178" t="n">
         <v>59.70000076293945</v>
@@ -5151,7 +5151,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>51.83636474609375</v>
+        <v>51.83637619018555</v>
       </c>
       <c r="C179" t="n">
         <v>56.11000061035156</v>
@@ -5180,7 +5180,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>53.3237419128418</v>
+        <v>53.32373428344727</v>
       </c>
       <c r="C180" t="n">
         <v>57.72000122070312</v>
@@ -5209,7 +5209,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>59.76287078857422</v>
+        <v>59.76287460327148</v>
       </c>
       <c r="C181" t="n">
         <v>64.69000244140625</v>
@@ -5238,7 +5238,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>56.04096603393555</v>
+        <v>56.04095458984375</v>
       </c>
       <c r="C182" t="n">
         <v>60.43000030517578</v>
@@ -5267,7 +5267,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>59.82463073730469</v>
+        <v>59.82462692260742</v>
       </c>
       <c r="C183" t="n">
         <v>64.51000213623047</v>
@@ -5296,7 +5296,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>65.07353210449219</v>
+        <v>65.07353973388672</v>
       </c>
       <c r="C184" t="n">
         <v>70.16999816894531</v>
@@ -5325,7 +5325,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>70.58946228027344</v>
+        <v>70.58946990966797</v>
       </c>
       <c r="C185" t="n">
         <v>75.79000091552734</v>
@@ -5412,7 +5412,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>81.46003723144531</v>
+        <v>81.46002197265625</v>
       </c>
       <c r="C188" t="n">
         <v>87.13999938964844</v>
@@ -5441,7 +5441,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>83.32032775878906</v>
+        <v>83.32032012939453</v>
       </c>
       <c r="C189" t="n">
         <v>89.12999725341797</v>
@@ -5470,7 +5470,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>81.45069885253906</v>
+        <v>81.45070648193359</v>
       </c>
       <c r="C190" t="n">
         <v>87.12999725341797</v>
@@ -5528,7 +5528,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>85.12046051025391</v>
+        <v>85.12046813964844</v>
       </c>
       <c r="C192" t="n">
         <v>90.73999786376953</v>
@@ -5557,7 +5557,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>81.80906677246094</v>
+        <v>81.80907440185547</v>
       </c>
       <c r="C193" t="n">
         <v>87.20999908447266</v>
@@ -5615,7 +5615,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>71.52989959716797</v>
+        <v>71.52991485595703</v>
       </c>
       <c r="C195" t="n">
         <v>75.97000122070312</v>
@@ -5673,7 +5673,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>69.38047027587891</v>
+        <v>69.3804931640625</v>
       </c>
       <c r="C197" t="n">
         <v>73.40000152587891</v>
@@ -5702,7 +5702,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>67.98150634765625</v>
+        <v>67.98152160644531</v>
       </c>
       <c r="C198" t="n">
         <v>71.91999816894531</v>
@@ -5731,7 +5731,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>66.04378509521484</v>
+        <v>66.04379272460938</v>
       </c>
       <c r="C199" t="n">
         <v>69.87000274658203</v>
@@ -5818,7 +5818,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>57.98385620117188</v>
+        <v>57.98386001586914</v>
       </c>
       <c r="C202" t="n">
         <v>61.06999969482422</v>
@@ -5876,7 +5876,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>79.23936462402344</v>
+        <v>79.23937225341797</v>
       </c>
       <c r="C204" t="n">
         <v>83.02999877929688</v>
@@ -5905,7 +5905,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>78.00823974609375</v>
+        <v>78.00825500488281</v>
       </c>
       <c r="C205" t="n">
         <v>81.73999786376953</v>
@@ -5934,7 +5934,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>84.738037109375</v>
+        <v>84.73802947998047</v>
       </c>
       <c r="C206" t="n">
         <v>88.45999908447266</v>
@@ -5963,7 +5963,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>83.72263336181641</v>
+        <v>83.72261810302734</v>
       </c>
       <c r="C207" t="n">
         <v>87.40000152587891</v>
@@ -5992,7 +5992,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>89.01038360595703</v>
+        <v>89.01036834716797</v>
       </c>
       <c r="C208" t="n">
         <v>92.91999816894531</v>
@@ -6021,7 +6021,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>91.11459350585938</v>
+        <v>91.11460876464844</v>
       </c>
       <c r="C209" t="n">
         <v>94.72000122070312</v>
@@ -6079,7 +6079,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>114.5569763183594</v>
+        <v>114.5569686889648</v>
       </c>
       <c r="C211" t="n">
         <v>119.0899963378906</v>
@@ -6108,7 +6108,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>113.1635437011719</v>
+        <v>113.1635208129883</v>
       </c>
       <c r="C212" t="n">
         <v>117.2300033569336</v>
@@ -6137,7 +6137,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>116.2139053344727</v>
+        <v>116.2139205932617</v>
       </c>
       <c r="C213" t="n">
         <v>120.3899993896484</v>
@@ -6166,7 +6166,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>102.2458572387695</v>
+        <v>102.2458419799805</v>
       </c>
       <c r="C214" t="n">
         <v>105.9199981689453</v>
@@ -6195,7 +6195,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>100.1785049438477</v>
+        <v>100.1785125732422</v>
       </c>
       <c r="C215" t="n">
         <v>103.4000015258789</v>
@@ -6253,7 +6253,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>102.1452560424805</v>
+        <v>102.1452484130859</v>
       </c>
       <c r="C217" t="n">
         <v>105.4300003051758</v>
@@ -6282,7 +6282,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>108.6392517089844</v>
+        <v>108.6392288208008</v>
       </c>
       <c r="C218" t="n">
         <v>111.6999969482422</v>
@@ -6311,7 +6311,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>108.6197891235352</v>
+        <v>108.6198043823242</v>
       </c>
       <c r="C219" t="n">
         <v>111.6800003051758</v>
@@ -6340,7 +6340,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>122.168098449707</v>
+        <v>122.1680908203125</v>
       </c>
       <c r="C220" t="n">
         <v>125.6100006103516</v>
@@ -6369,7 +6369,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>110.990104675293</v>
+        <v>110.9901123046875</v>
       </c>
       <c r="C221" t="n">
         <v>113.75</v>
@@ -6427,7 +6427,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>137.7741088867188</v>
+        <v>137.7740783691406</v>
       </c>
       <c r="C223" t="n">
         <v>141.1999969482422</v>
@@ -6485,7 +6485,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>138.2511444091797</v>
+        <v>138.2511596679688</v>
       </c>
       <c r="C225" t="n">
         <v>141.2899932861328</v>
@@ -6514,7 +6514,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>166.7350463867188</v>
+        <v>166.7350311279297</v>
       </c>
       <c r="C226" t="n">
         <v>170.3999938964844</v>
@@ -6543,7 +6543,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>164.5993804931641</v>
+        <v>164.5993957519531</v>
       </c>
       <c r="C227" t="n">
         <v>167.8399963378906</v>
@@ -6572,7 +6572,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>181.2711639404297</v>
+        <v>181.2711791992188</v>
       </c>
       <c r="C228" t="n">
         <v>184.8399963378906</v>
@@ -6601,7 +6601,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>163.4225616455078</v>
+        <v>163.4225769042969</v>
       </c>
       <c r="C229" t="n">
         <v>166.6399993896484</v>
@@ -6630,7 +6630,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>167.1864624023438</v>
+        <v>167.1864471435547</v>
       </c>
       <c r="C230" t="n">
         <v>170.0599975585938</v>
@@ -6659,7 +6659,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>163.2540283203125</v>
+        <v>163.2540435791016</v>
       </c>
       <c r="C231" t="n">
         <v>166.0599975585938</v>
@@ -6688,7 +6688,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>137.4476165771484</v>
+        <v>137.4476013183594</v>
       </c>
       <c r="C232" t="n">
         <v>139.8099975585938</v>
@@ -6717,7 +6717,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>138.8391876220703</v>
+        <v>138.8391723632812</v>
       </c>
       <c r="C233" t="n">
         <v>140.7200012207031</v>
@@ -6746,7 +6746,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>163.3175659179688</v>
+        <v>163.3175811767578</v>
       </c>
       <c r="C234" t="n">
         <v>165.5299987792969</v>
@@ -6775,7 +6775,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>215.7078857421875</v>
+        <v>215.7078704833984</v>
       </c>
       <c r="C235" t="n">
         <v>218.6300048828125</v>
@@ -6891,7 +6891,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>260.1011962890625</v>
+        <v>260.1011657714844</v>
       </c>
       <c r="C239" t="n">
         <v>262.6099853515625</v>
@@ -6920,7 +6920,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>200.0206909179688</v>
+        <v>200.0206756591797</v>
       </c>
       <c r="C240" t="n">
         <v>201.9499969482422</v>
